--- a/temp/template_staff.xlsx
+++ b/temp/template_staff.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mizuno\Dailyreport_test\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8AEDB8-2819-4D80-9495-517D263EE65F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D47D0A-AF71-4D4E-A0F7-C34005848CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29340" yWindow="690" windowWidth="27735" windowHeight="15150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="temp_staff" sheetId="33" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="52">
   <si>
     <t>21</t>
   </si>
@@ -215,16 +215,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>業務種別</t>
-    <rPh sb="0" eb="2">
-      <t>ギョウム</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>シュベツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>工事番号別</t>
     <rPh sb="0" eb="2">
       <t>コウジ</t>
@@ -290,6 +280,27 @@
     </rPh>
     <rPh sb="3" eb="5">
       <t>ソウム</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>業務種別</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>現場搬入</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンバ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハンニュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>搬出</t>
+    <rPh sb="0" eb="2">
+      <t>ハンシュツ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -486,7 +497,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -565,6 +576,9 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -912,51 +926,51 @@
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="A1:AR36"/>
+  <dimension ref="A1:AT36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
     <col min="2" max="2" width="15.75" style="22" customWidth="1"/>
-    <col min="3" max="13" width="11.875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="1" style="6" customWidth="1"/>
-    <col min="15" max="15" width="11.125" style="6" customWidth="1"/>
-    <col min="16" max="18" width="11.125" style="2" customWidth="1"/>
-    <col min="19" max="26" width="11.125" style="6" customWidth="1"/>
-    <col min="27" max="35" width="5.375" style="6" customWidth="1"/>
-    <col min="36" max="44" width="5.375" style="2" customWidth="1"/>
-    <col min="45" max="16384" width="9" style="2"/>
+    <col min="3" max="15" width="11.875" style="2" customWidth="1"/>
+    <col min="16" max="16" width="1" style="6" customWidth="1"/>
+    <col min="17" max="17" width="11.125" style="6" customWidth="1"/>
+    <col min="18" max="20" width="11.125" style="2" customWidth="1"/>
+    <col min="21" max="28" width="11.125" style="6" customWidth="1"/>
+    <col min="29" max="37" width="5.375" style="6" customWidth="1"/>
+    <col min="38" max="46" width="5.375" style="2" customWidth="1"/>
+    <col min="47" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:46" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="25"/>
       <c r="B1" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C1" s="16"/>
       <c r="D1" s="20" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E1" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="17"/>
+      <c r="F1" s="27"/>
       <c r="G1" s="17"/>
       <c r="H1" s="17"/>
       <c r="I1" s="17"/>
       <c r="J1" s="17"/>
       <c r="K1" s="17"/>
       <c r="L1" s="17"/>
-      <c r="M1" s="18"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q1" s="14" t="s">
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="18"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="S1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="R1" s="9"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="10"/>
+      <c r="T1" s="9"/>
       <c r="U1" s="10"/>
       <c r="V1" s="10"/>
       <c r="W1" s="10"/>
@@ -981,47 +995,53 @@
       <c r="AP1" s="10"/>
       <c r="AQ1" s="10"/>
       <c r="AR1" s="10"/>
-    </row>
-    <row r="2" spans="1:44" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS1" s="10"/>
+      <c r="AT1" s="10"/>
+    </row>
+    <row r="2" spans="1:46" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="26"/>
       <c r="B2" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C2" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="I2" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="H2" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="I2" s="13" t="s">
+      <c r="L2" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="J2" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="K2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
@@ -1051,8 +1071,10 @@
       <c r="AP2" s="4"/>
       <c r="AQ2" s="4"/>
       <c r="AR2" s="4"/>
-    </row>
-    <row r="3" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS2" s="4"/>
+      <c r="AT2" s="4"/>
+    </row>
+    <row r="3" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -1068,9 +1090,9 @@
       <c r="K3" s="24"/>
       <c r="L3" s="24"/>
       <c r="M3" s="24"/>
-      <c r="N3" s="8"/>
+      <c r="N3" s="24"/>
       <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
+      <c r="P3" s="8"/>
       <c r="Q3" s="24"/>
       <c r="R3" s="24"/>
       <c r="S3" s="24"/>
@@ -1099,8 +1121,10 @@
       <c r="AP3" s="24"/>
       <c r="AQ3" s="24"/>
       <c r="AR3" s="24"/>
-    </row>
-    <row r="4" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS3" s="24"/>
+      <c r="AT3" s="24"/>
+    </row>
+    <row r="4" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
@@ -1116,9 +1140,9 @@
       <c r="K4" s="24"/>
       <c r="L4" s="24"/>
       <c r="M4" s="24"/>
-      <c r="N4" s="8"/>
+      <c r="N4" s="24"/>
       <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
+      <c r="P4" s="8"/>
       <c r="Q4" s="24"/>
       <c r="R4" s="24"/>
       <c r="S4" s="24"/>
@@ -1147,8 +1171,10 @@
       <c r="AP4" s="24"/>
       <c r="AQ4" s="24"/>
       <c r="AR4" s="24"/>
-    </row>
-    <row r="5" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS4" s="24"/>
+      <c r="AT4" s="24"/>
+    </row>
+    <row r="5" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="5" t="s">
         <v>2</v>
       </c>
@@ -1164,9 +1190,9 @@
       <c r="K5" s="24"/>
       <c r="L5" s="24"/>
       <c r="M5" s="24"/>
-      <c r="N5" s="8"/>
+      <c r="N5" s="24"/>
       <c r="O5" s="24"/>
-      <c r="P5" s="24"/>
+      <c r="P5" s="8"/>
       <c r="Q5" s="24"/>
       <c r="R5" s="24"/>
       <c r="S5" s="24"/>
@@ -1195,8 +1221,10 @@
       <c r="AP5" s="24"/>
       <c r="AQ5" s="24"/>
       <c r="AR5" s="24"/>
-    </row>
-    <row r="6" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS5" s="24"/>
+      <c r="AT5" s="24"/>
+    </row>
+    <row r="6" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5" t="s">
         <v>3</v>
       </c>
@@ -1212,9 +1240,9 @@
       <c r="K6" s="24"/>
       <c r="L6" s="24"/>
       <c r="M6" s="24"/>
-      <c r="N6" s="8"/>
+      <c r="N6" s="24"/>
       <c r="O6" s="24"/>
-      <c r="P6" s="24"/>
+      <c r="P6" s="8"/>
       <c r="Q6" s="24"/>
       <c r="R6" s="24"/>
       <c r="S6" s="24"/>
@@ -1243,8 +1271,10 @@
       <c r="AP6" s="24"/>
       <c r="AQ6" s="24"/>
       <c r="AR6" s="24"/>
-    </row>
-    <row r="7" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS6" s="24"/>
+      <c r="AT6" s="24"/>
+    </row>
+    <row r="7" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="5" t="s">
         <v>4</v>
       </c>
@@ -1260,9 +1290,9 @@
       <c r="K7" s="24"/>
       <c r="L7" s="24"/>
       <c r="M7" s="24"/>
-      <c r="N7" s="8"/>
+      <c r="N7" s="24"/>
       <c r="O7" s="24"/>
-      <c r="P7" s="24"/>
+      <c r="P7" s="8"/>
       <c r="Q7" s="24"/>
       <c r="R7" s="24"/>
       <c r="S7" s="24"/>
@@ -1291,8 +1321,10 @@
       <c r="AP7" s="24"/>
       <c r="AQ7" s="24"/>
       <c r="AR7" s="24"/>
-    </row>
-    <row r="8" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS7" s="24"/>
+      <c r="AT7" s="24"/>
+    </row>
+    <row r="8" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
@@ -1308,9 +1340,9 @@
       <c r="K8" s="24"/>
       <c r="L8" s="24"/>
       <c r="M8" s="24"/>
-      <c r="N8" s="8"/>
+      <c r="N8" s="24"/>
       <c r="O8" s="24"/>
-      <c r="P8" s="24"/>
+      <c r="P8" s="8"/>
       <c r="Q8" s="24"/>
       <c r="R8" s="24"/>
       <c r="S8" s="24"/>
@@ -1339,8 +1371,10 @@
       <c r="AP8" s="24"/>
       <c r="AQ8" s="24"/>
       <c r="AR8" s="24"/>
-    </row>
-    <row r="9" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS8" s="24"/>
+      <c r="AT8" s="24"/>
+    </row>
+    <row r="9" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="5" t="s">
         <v>6</v>
       </c>
@@ -1356,9 +1390,9 @@
       <c r="K9" s="24"/>
       <c r="L9" s="24"/>
       <c r="M9" s="24"/>
-      <c r="N9" s="8"/>
+      <c r="N9" s="24"/>
       <c r="O9" s="24"/>
-      <c r="P9" s="24"/>
+      <c r="P9" s="8"/>
       <c r="Q9" s="24"/>
       <c r="R9" s="24"/>
       <c r="S9" s="24"/>
@@ -1387,8 +1421,10 @@
       <c r="AP9" s="24"/>
       <c r="AQ9" s="24"/>
       <c r="AR9" s="24"/>
-    </row>
-    <row r="10" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS9" s="24"/>
+      <c r="AT9" s="24"/>
+    </row>
+    <row r="10" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="5" t="s">
         <v>7</v>
       </c>
@@ -1404,9 +1440,9 @@
       <c r="K10" s="24"/>
       <c r="L10" s="24"/>
       <c r="M10" s="24"/>
-      <c r="N10" s="8"/>
+      <c r="N10" s="24"/>
       <c r="O10" s="24"/>
-      <c r="P10" s="24"/>
+      <c r="P10" s="8"/>
       <c r="Q10" s="24"/>
       <c r="R10" s="24"/>
       <c r="S10" s="24"/>
@@ -1435,8 +1471,10 @@
       <c r="AP10" s="24"/>
       <c r="AQ10" s="24"/>
       <c r="AR10" s="24"/>
-    </row>
-    <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS10" s="24"/>
+      <c r="AT10" s="24"/>
+    </row>
+    <row r="11" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="5" t="s">
         <v>8</v>
       </c>
@@ -1452,9 +1490,9 @@
       <c r="K11" s="24"/>
       <c r="L11" s="24"/>
       <c r="M11" s="24"/>
-      <c r="N11" s="8"/>
+      <c r="N11" s="24"/>
       <c r="O11" s="24"/>
-      <c r="P11" s="24"/>
+      <c r="P11" s="8"/>
       <c r="Q11" s="24"/>
       <c r="R11" s="24"/>
       <c r="S11" s="24"/>
@@ -1483,8 +1521,10 @@
       <c r="AP11" s="24"/>
       <c r="AQ11" s="24"/>
       <c r="AR11" s="24"/>
-    </row>
-    <row r="12" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS11" s="24"/>
+      <c r="AT11" s="24"/>
+    </row>
+    <row r="12" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="5" t="s">
         <v>9</v>
       </c>
@@ -1500,9 +1540,9 @@
       <c r="K12" s="24"/>
       <c r="L12" s="24"/>
       <c r="M12" s="24"/>
-      <c r="N12" s="8"/>
+      <c r="N12" s="24"/>
       <c r="O12" s="24"/>
-      <c r="P12" s="24"/>
+      <c r="P12" s="8"/>
       <c r="Q12" s="24"/>
       <c r="R12" s="24"/>
       <c r="S12" s="24"/>
@@ -1531,8 +1571,10 @@
       <c r="AP12" s="24"/>
       <c r="AQ12" s="24"/>
       <c r="AR12" s="24"/>
-    </row>
-    <row r="13" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS12" s="24"/>
+      <c r="AT12" s="24"/>
+    </row>
+    <row r="13" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="5" t="s">
         <v>10</v>
       </c>
@@ -1548,9 +1590,9 @@
       <c r="K13" s="24"/>
       <c r="L13" s="24"/>
       <c r="M13" s="24"/>
-      <c r="N13" s="8"/>
+      <c r="N13" s="24"/>
       <c r="O13" s="24"/>
-      <c r="P13" s="24"/>
+      <c r="P13" s="8"/>
       <c r="Q13" s="24"/>
       <c r="R13" s="24"/>
       <c r="S13" s="24"/>
@@ -1579,8 +1621,10 @@
       <c r="AP13" s="24"/>
       <c r="AQ13" s="24"/>
       <c r="AR13" s="24"/>
-    </row>
-    <row r="14" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS13" s="24"/>
+      <c r="AT13" s="24"/>
+    </row>
+    <row r="14" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="5" t="s">
         <v>11</v>
       </c>
@@ -1596,9 +1640,9 @@
       <c r="K14" s="24"/>
       <c r="L14" s="24"/>
       <c r="M14" s="24"/>
-      <c r="N14" s="8"/>
+      <c r="N14" s="24"/>
       <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
+      <c r="P14" s="8"/>
       <c r="Q14" s="24"/>
       <c r="R14" s="24"/>
       <c r="S14" s="24"/>
@@ -1627,8 +1671,10 @@
       <c r="AP14" s="24"/>
       <c r="AQ14" s="24"/>
       <c r="AR14" s="24"/>
-    </row>
-    <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS14" s="24"/>
+      <c r="AT14" s="24"/>
+    </row>
+    <row r="15" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="5" t="s">
         <v>12</v>
       </c>
@@ -1644,9 +1690,9 @@
       <c r="K15" s="24"/>
       <c r="L15" s="24"/>
       <c r="M15" s="24"/>
-      <c r="N15" s="8"/>
+      <c r="N15" s="24"/>
       <c r="O15" s="24"/>
-      <c r="P15" s="24"/>
+      <c r="P15" s="8"/>
       <c r="Q15" s="24"/>
       <c r="R15" s="24"/>
       <c r="S15" s="24"/>
@@ -1675,8 +1721,10 @@
       <c r="AP15" s="24"/>
       <c r="AQ15" s="24"/>
       <c r="AR15" s="24"/>
-    </row>
-    <row r="16" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS15" s="24"/>
+      <c r="AT15" s="24"/>
+    </row>
+    <row r="16" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="5" t="s">
         <v>13</v>
       </c>
@@ -1692,9 +1740,9 @@
       <c r="K16" s="24"/>
       <c r="L16" s="24"/>
       <c r="M16" s="24"/>
-      <c r="N16" s="8"/>
+      <c r="N16" s="24"/>
       <c r="O16" s="24"/>
-      <c r="P16" s="24"/>
+      <c r="P16" s="8"/>
       <c r="Q16" s="24"/>
       <c r="R16" s="24"/>
       <c r="S16" s="24"/>
@@ -1723,8 +1771,10 @@
       <c r="AP16" s="24"/>
       <c r="AQ16" s="24"/>
       <c r="AR16" s="24"/>
-    </row>
-    <row r="17" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS16" s="24"/>
+      <c r="AT16" s="24"/>
+    </row>
+    <row r="17" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="5" t="s">
         <v>14</v>
       </c>
@@ -1740,9 +1790,9 @@
       <c r="K17" s="24"/>
       <c r="L17" s="24"/>
       <c r="M17" s="24"/>
-      <c r="N17" s="8"/>
+      <c r="N17" s="24"/>
       <c r="O17" s="24"/>
-      <c r="P17" s="24"/>
+      <c r="P17" s="8"/>
       <c r="Q17" s="24"/>
       <c r="R17" s="24"/>
       <c r="S17" s="24"/>
@@ -1771,8 +1821,10 @@
       <c r="AP17" s="24"/>
       <c r="AQ17" s="24"/>
       <c r="AR17" s="24"/>
-    </row>
-    <row r="18" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS17" s="24"/>
+      <c r="AT17" s="24"/>
+    </row>
+    <row r="18" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="5" t="s">
         <v>15</v>
       </c>
@@ -1788,9 +1840,9 @@
       <c r="K18" s="24"/>
       <c r="L18" s="24"/>
       <c r="M18" s="24"/>
-      <c r="N18" s="8"/>
+      <c r="N18" s="24"/>
       <c r="O18" s="24"/>
-      <c r="P18" s="24"/>
+      <c r="P18" s="8"/>
       <c r="Q18" s="24"/>
       <c r="R18" s="24"/>
       <c r="S18" s="24"/>
@@ -1819,8 +1871,10 @@
       <c r="AP18" s="24"/>
       <c r="AQ18" s="24"/>
       <c r="AR18" s="24"/>
-    </row>
-    <row r="19" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS18" s="24"/>
+      <c r="AT18" s="24"/>
+    </row>
+    <row r="19" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="5" t="s">
         <v>16</v>
       </c>
@@ -1836,9 +1890,9 @@
       <c r="K19" s="24"/>
       <c r="L19" s="24"/>
       <c r="M19" s="24"/>
-      <c r="N19" s="8"/>
+      <c r="N19" s="24"/>
       <c r="O19" s="24"/>
-      <c r="P19" s="24"/>
+      <c r="P19" s="8"/>
       <c r="Q19" s="24"/>
       <c r="R19" s="24"/>
       <c r="S19" s="24"/>
@@ -1867,8 +1921,10 @@
       <c r="AP19" s="24"/>
       <c r="AQ19" s="24"/>
       <c r="AR19" s="24"/>
-    </row>
-    <row r="20" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS19" s="24"/>
+      <c r="AT19" s="24"/>
+    </row>
+    <row r="20" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="5" t="s">
         <v>17</v>
       </c>
@@ -1884,9 +1940,9 @@
       <c r="K20" s="24"/>
       <c r="L20" s="24"/>
       <c r="M20" s="24"/>
-      <c r="N20" s="8"/>
+      <c r="N20" s="24"/>
       <c r="O20" s="24"/>
-      <c r="P20" s="24"/>
+      <c r="P20" s="8"/>
       <c r="Q20" s="24"/>
       <c r="R20" s="24"/>
       <c r="S20" s="24"/>
@@ -1915,8 +1971,10 @@
       <c r="AP20" s="24"/>
       <c r="AQ20" s="24"/>
       <c r="AR20" s="24"/>
-    </row>
-    <row r="21" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS20" s="24"/>
+      <c r="AT20" s="24"/>
+    </row>
+    <row r="21" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="5" t="s">
         <v>18</v>
       </c>
@@ -1932,9 +1990,9 @@
       <c r="K21" s="24"/>
       <c r="L21" s="24"/>
       <c r="M21" s="24"/>
-      <c r="N21" s="8"/>
+      <c r="N21" s="24"/>
       <c r="O21" s="24"/>
-      <c r="P21" s="24"/>
+      <c r="P21" s="8"/>
       <c r="Q21" s="24"/>
       <c r="R21" s="24"/>
       <c r="S21" s="24"/>
@@ -1963,8 +2021,10 @@
       <c r="AP21" s="24"/>
       <c r="AQ21" s="24"/>
       <c r="AR21" s="24"/>
-    </row>
-    <row r="22" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS21" s="24"/>
+      <c r="AT21" s="24"/>
+    </row>
+    <row r="22" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="5" t="s">
         <v>19</v>
       </c>
@@ -1980,9 +2040,9 @@
       <c r="K22" s="24"/>
       <c r="L22" s="24"/>
       <c r="M22" s="24"/>
-      <c r="N22" s="8"/>
+      <c r="N22" s="24"/>
       <c r="O22" s="24"/>
-      <c r="P22" s="24"/>
+      <c r="P22" s="8"/>
       <c r="Q22" s="24"/>
       <c r="R22" s="24"/>
       <c r="S22" s="24"/>
@@ -2011,8 +2071,10 @@
       <c r="AP22" s="24"/>
       <c r="AQ22" s="24"/>
       <c r="AR22" s="24"/>
-    </row>
-    <row r="23" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS22" s="24"/>
+      <c r="AT22" s="24"/>
+    </row>
+    <row r="23" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="5" t="s">
         <v>20</v>
       </c>
@@ -2028,9 +2090,9 @@
       <c r="K23" s="24"/>
       <c r="L23" s="24"/>
       <c r="M23" s="24"/>
-      <c r="N23" s="8"/>
+      <c r="N23" s="24"/>
       <c r="O23" s="24"/>
-      <c r="P23" s="24"/>
+      <c r="P23" s="8"/>
       <c r="Q23" s="24"/>
       <c r="R23" s="24"/>
       <c r="S23" s="24"/>
@@ -2059,8 +2121,10 @@
       <c r="AP23" s="24"/>
       <c r="AQ23" s="24"/>
       <c r="AR23" s="24"/>
-    </row>
-    <row r="24" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS23" s="24"/>
+      <c r="AT23" s="24"/>
+    </row>
+    <row r="24" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="5" t="s">
         <v>21</v>
       </c>
@@ -2076,9 +2140,9 @@
       <c r="K24" s="24"/>
       <c r="L24" s="24"/>
       <c r="M24" s="24"/>
-      <c r="N24" s="8"/>
+      <c r="N24" s="24"/>
       <c r="O24" s="24"/>
-      <c r="P24" s="24"/>
+      <c r="P24" s="8"/>
       <c r="Q24" s="24"/>
       <c r="R24" s="24"/>
       <c r="S24" s="24"/>
@@ -2107,8 +2171,10 @@
       <c r="AP24" s="24"/>
       <c r="AQ24" s="24"/>
       <c r="AR24" s="24"/>
-    </row>
-    <row r="25" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS24" s="24"/>
+      <c r="AT24" s="24"/>
+    </row>
+    <row r="25" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="5" t="s">
         <v>22</v>
       </c>
@@ -2124,9 +2190,9 @@
       <c r="K25" s="24"/>
       <c r="L25" s="24"/>
       <c r="M25" s="24"/>
-      <c r="N25" s="8"/>
+      <c r="N25" s="24"/>
       <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
+      <c r="P25" s="8"/>
       <c r="Q25" s="24"/>
       <c r="R25" s="24"/>
       <c r="S25" s="24"/>
@@ -2155,8 +2221,10 @@
       <c r="AP25" s="24"/>
       <c r="AQ25" s="24"/>
       <c r="AR25" s="24"/>
-    </row>
-    <row r="26" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS25" s="24"/>
+      <c r="AT25" s="24"/>
+    </row>
+    <row r="26" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="5" t="s">
         <v>23</v>
       </c>
@@ -2172,9 +2240,9 @@
       <c r="K26" s="24"/>
       <c r="L26" s="24"/>
       <c r="M26" s="24"/>
-      <c r="N26" s="8"/>
+      <c r="N26" s="24"/>
       <c r="O26" s="24"/>
-      <c r="P26" s="24"/>
+      <c r="P26" s="8"/>
       <c r="Q26" s="24"/>
       <c r="R26" s="24"/>
       <c r="S26" s="24"/>
@@ -2203,8 +2271,10 @@
       <c r="AP26" s="24"/>
       <c r="AQ26" s="24"/>
       <c r="AR26" s="24"/>
-    </row>
-    <row r="27" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS26" s="24"/>
+      <c r="AT26" s="24"/>
+    </row>
+    <row r="27" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="5" t="s">
         <v>24</v>
       </c>
@@ -2220,9 +2290,9 @@
       <c r="K27" s="24"/>
       <c r="L27" s="24"/>
       <c r="M27" s="24"/>
-      <c r="N27" s="8"/>
+      <c r="N27" s="24"/>
       <c r="O27" s="24"/>
-      <c r="P27" s="24"/>
+      <c r="P27" s="8"/>
       <c r="Q27" s="24"/>
       <c r="R27" s="24"/>
       <c r="S27" s="24"/>
@@ -2251,8 +2321,10 @@
       <c r="AP27" s="24"/>
       <c r="AQ27" s="24"/>
       <c r="AR27" s="24"/>
-    </row>
-    <row r="28" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS27" s="24"/>
+      <c r="AT27" s="24"/>
+    </row>
+    <row r="28" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="5" t="s">
         <v>25</v>
       </c>
@@ -2268,9 +2340,9 @@
       <c r="K28" s="24"/>
       <c r="L28" s="24"/>
       <c r="M28" s="24"/>
-      <c r="N28" s="8"/>
+      <c r="N28" s="24"/>
       <c r="O28" s="24"/>
-      <c r="P28" s="24"/>
+      <c r="P28" s="8"/>
       <c r="Q28" s="24"/>
       <c r="R28" s="24"/>
       <c r="S28" s="24"/>
@@ -2299,8 +2371,10 @@
       <c r="AP28" s="24"/>
       <c r="AQ28" s="24"/>
       <c r="AR28" s="24"/>
-    </row>
-    <row r="29" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS28" s="24"/>
+      <c r="AT28" s="24"/>
+    </row>
+    <row r="29" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="5" t="s">
         <v>26</v>
       </c>
@@ -2316,9 +2390,9 @@
       <c r="K29" s="24"/>
       <c r="L29" s="24"/>
       <c r="M29" s="24"/>
-      <c r="N29" s="8"/>
+      <c r="N29" s="24"/>
       <c r="O29" s="24"/>
-      <c r="P29" s="24"/>
+      <c r="P29" s="8"/>
       <c r="Q29" s="24"/>
       <c r="R29" s="24"/>
       <c r="S29" s="24"/>
@@ -2347,8 +2421,10 @@
       <c r="AP29" s="24"/>
       <c r="AQ29" s="24"/>
       <c r="AR29" s="24"/>
-    </row>
-    <row r="30" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS29" s="24"/>
+      <c r="AT29" s="24"/>
+    </row>
+    <row r="30" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="5" t="s">
         <v>27</v>
       </c>
@@ -2364,9 +2440,9 @@
       <c r="K30" s="24"/>
       <c r="L30" s="24"/>
       <c r="M30" s="24"/>
-      <c r="N30" s="8"/>
+      <c r="N30" s="24"/>
       <c r="O30" s="24"/>
-      <c r="P30" s="24"/>
+      <c r="P30" s="8"/>
       <c r="Q30" s="24"/>
       <c r="R30" s="24"/>
       <c r="S30" s="24"/>
@@ -2395,8 +2471,10 @@
       <c r="AP30" s="24"/>
       <c r="AQ30" s="24"/>
       <c r="AR30" s="24"/>
-    </row>
-    <row r="31" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS30" s="24"/>
+      <c r="AT30" s="24"/>
+    </row>
+    <row r="31" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="5" t="s">
         <v>28</v>
       </c>
@@ -2412,9 +2490,9 @@
       <c r="K31" s="24"/>
       <c r="L31" s="24"/>
       <c r="M31" s="24"/>
-      <c r="N31" s="8"/>
+      <c r="N31" s="24"/>
       <c r="O31" s="24"/>
-      <c r="P31" s="24"/>
+      <c r="P31" s="8"/>
       <c r="Q31" s="24"/>
       <c r="R31" s="24"/>
       <c r="S31" s="24"/>
@@ -2443,8 +2521,10 @@
       <c r="AP31" s="24"/>
       <c r="AQ31" s="24"/>
       <c r="AR31" s="24"/>
-    </row>
-    <row r="32" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS31" s="24"/>
+      <c r="AT31" s="24"/>
+    </row>
+    <row r="32" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="5" t="s">
         <v>29</v>
       </c>
@@ -2460,9 +2540,9 @@
       <c r="K32" s="24"/>
       <c r="L32" s="24"/>
       <c r="M32" s="24"/>
-      <c r="N32" s="8"/>
+      <c r="N32" s="24"/>
       <c r="O32" s="24"/>
-      <c r="P32" s="24"/>
+      <c r="P32" s="8"/>
       <c r="Q32" s="24"/>
       <c r="R32" s="24"/>
       <c r="S32" s="24"/>
@@ -2491,8 +2571,10 @@
       <c r="AP32" s="24"/>
       <c r="AQ32" s="24"/>
       <c r="AR32" s="24"/>
-    </row>
-    <row r="33" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS32" s="24"/>
+      <c r="AT32" s="24"/>
+    </row>
+    <row r="33" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="5" t="s">
         <v>30</v>
       </c>
@@ -2508,9 +2590,9 @@
       <c r="K33" s="24"/>
       <c r="L33" s="24"/>
       <c r="M33" s="24"/>
-      <c r="N33" s="8"/>
+      <c r="N33" s="24"/>
       <c r="O33" s="24"/>
-      <c r="P33" s="24"/>
+      <c r="P33" s="8"/>
       <c r="Q33" s="24"/>
       <c r="R33" s="24"/>
       <c r="S33" s="24"/>
@@ -2539,8 +2621,10 @@
       <c r="AP33" s="24"/>
       <c r="AQ33" s="24"/>
       <c r="AR33" s="24"/>
-    </row>
-    <row r="34" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS33" s="24"/>
+      <c r="AT33" s="24"/>
+    </row>
+    <row r="34" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="3" t="s">
         <v>31</v>
       </c>
@@ -2556,18 +2640,18 @@
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
       <c r="J34" s="11"/>
-      <c r="K34" s="11" t="s">
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="L34" s="11"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="7"/>
-      <c r="O34" s="11"/>
-      <c r="P34" s="11"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="7"/>
+      <c r="P34" s="7"/>
       <c r="Q34" s="11"/>
       <c r="R34" s="11"/>
-      <c r="S34" s="7"/>
-      <c r="T34" s="7"/>
+      <c r="S34" s="11"/>
+      <c r="T34" s="11"/>
       <c r="U34" s="7"/>
       <c r="V34" s="7"/>
       <c r="W34" s="7"/>
@@ -2583,8 +2667,8 @@
       <c r="AG34" s="7"/>
       <c r="AH34" s="7"/>
       <c r="AI34" s="7"/>
-      <c r="AJ34" s="11"/>
-      <c r="AK34" s="11"/>
+      <c r="AJ34" s="7"/>
+      <c r="AK34" s="7"/>
       <c r="AL34" s="11"/>
       <c r="AM34" s="11"/>
       <c r="AN34" s="11"/>
@@ -2592,8 +2676,10 @@
       <c r="AP34" s="11"/>
       <c r="AQ34" s="11"/>
       <c r="AR34" s="11"/>
-    </row>
-    <row r="35" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS34" s="11"/>
+      <c r="AT34" s="11"/>
+    </row>
+    <row r="35" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
         <v>32</v>
       </c>
@@ -2601,7 +2687,6 @@
         <f>B34*5360</f>
         <v>0</v>
       </c>
-      <c r="D35" s="11"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="11"/>
@@ -2610,14 +2695,14 @@
       <c r="J35" s="11"/>
       <c r="K35" s="11"/>
       <c r="L35" s="11"/>
-      <c r="M35" s="7"/>
-      <c r="N35" s="7"/>
-      <c r="O35" s="11"/>
-      <c r="P35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="7"/>
+      <c r="P35" s="7"/>
       <c r="Q35" s="11"/>
       <c r="R35" s="11"/>
-      <c r="S35" s="7"/>
-      <c r="T35" s="7"/>
+      <c r="S35" s="11"/>
+      <c r="T35" s="11"/>
       <c r="U35" s="7"/>
       <c r="V35" s="7"/>
       <c r="W35" s="7"/>
@@ -2633,8 +2718,8 @@
       <c r="AG35" s="7"/>
       <c r="AH35" s="7"/>
       <c r="AI35" s="7"/>
-      <c r="AJ35" s="11"/>
-      <c r="AK35" s="11"/>
+      <c r="AJ35" s="7"/>
+      <c r="AK35" s="7"/>
       <c r="AL35" s="11"/>
       <c r="AM35" s="11"/>
       <c r="AN35" s="11"/>
@@ -2642,10 +2727,12 @@
       <c r="AP35" s="11"/>
       <c r="AQ35" s="11"/>
       <c r="AR35" s="11"/>
-    </row>
-    <row r="36" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AS35" s="11"/>
+      <c r="AT35" s="11"/>
+    </row>
+    <row r="36" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C36" s="11"/>
-      <c r="E36" s="11"/>
+      <c r="D36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="11"/>
       <c r="H36" s="11"/>
@@ -2653,14 +2740,14 @@
       <c r="J36" s="11"/>
       <c r="K36" s="11"/>
       <c r="L36" s="11"/>
-      <c r="M36" s="7"/>
-      <c r="N36" s="7"/>
-      <c r="O36" s="11"/>
-      <c r="P36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="7"/>
+      <c r="P36" s="7"/>
       <c r="Q36" s="11"/>
       <c r="R36" s="11"/>
-      <c r="S36" s="7"/>
-      <c r="T36" s="7"/>
+      <c r="S36" s="11"/>
+      <c r="T36" s="11"/>
       <c r="U36" s="7"/>
       <c r="V36" s="7"/>
       <c r="W36" s="7"/>
@@ -2676,8 +2763,8 @@
       <c r="AG36" s="7"/>
       <c r="AH36" s="7"/>
       <c r="AI36" s="7"/>
-      <c r="AJ36" s="11"/>
-      <c r="AK36" s="11"/>
+      <c r="AJ36" s="7"/>
+      <c r="AK36" s="7"/>
       <c r="AL36" s="11"/>
       <c r="AM36" s="11"/>
       <c r="AN36" s="11"/>
@@ -2685,6 +2772,8 @@
       <c r="AP36" s="11"/>
       <c r="AQ36" s="11"/>
       <c r="AR36" s="11"/>
+      <c r="AS36" s="11"/>
+      <c r="AT36" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
